--- a/data/poi.xlsx
+++ b/data/poi.xlsx
@@ -448,7 +448,7 @@
         <v>Đồi Mâm Xôi - La Pán Tẩn</v>
       </c>
       <c r="C2" t="str">
-        <v>ruong_bac_thang</v>
+        <v>diem_ngam_canh</v>
       </c>
       <c r="D2" t="str">
         <v>La Pán Tẩn</v>
@@ -489,7 +489,7 @@
         <v>Ruộng bậc thang Chế Cu Nha</v>
       </c>
       <c r="C3" t="str">
-        <v>ruong_bac_thang</v>
+        <v>diem_ngam_canh</v>
       </c>
       <c r="D3" t="str">
         <v>Chế Cu Nha</v>
@@ -530,7 +530,7 @@
         <v>Ruộng bậc thang Dế Xu Phình</v>
       </c>
       <c r="C4" t="str">
-        <v>ruong_bac_thang</v>
+        <v>diem_ngam_canh</v>
       </c>
       <c r="D4" t="str">
         <v>Dế Xu Phình</v>
@@ -776,7 +776,7 @@
         <v>Chợ phiên Mù Cang Chải</v>
       </c>
       <c r="C10" t="str">
-        <v>le_hoi</v>
+        <v>diem_ngam_canh</v>
       </c>
       <c r="D10" t="str">
         <v>Thị trấn Mù Cang Chải</v>
@@ -817,7 +817,7 @@
         <v>Tuần Văn hóa Du lịch Mù Cang Chải</v>
       </c>
       <c r="C11" t="str">
-        <v>le_hoi</v>
+        <v>diem_ngam_canh</v>
       </c>
       <c r="D11" t="str">
         <v>Thị trấn Mù Cang Chải</v>
@@ -858,7 +858,7 @@
         <v>Xôi ngũ sắc &amp; cơm lam Mù Cang Chải</v>
       </c>
       <c r="C12" t="str">
-        <v>dac_san</v>
+        <v>nha_hang</v>
       </c>
       <c r="D12" t="str">
         <v>Thị trấn Mù Cang Chải</v>
